--- a/src/assets/worklog/09.Stacking.xlsx
+++ b/src/assets/worklog/09.Stacking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\data\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398AB975-FE56-4A15-ADB8-F9FA899343D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0B3486-ECBE-4A40-BA0F-77739C0B5477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17100" yWindow="390" windowWidth="19140" windowHeight="15210" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
+    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
     <definedName name="line">원본!$C$9</definedName>
     <definedName name="manufactureDate">원본!$C$7</definedName>
     <definedName name="plant">원본!$G$9</definedName>
-    <definedName name="productionId">원본!$G$7</definedName>
+    <definedName name="projectId">원본!$G$7</definedName>
     <definedName name="remark">원본!$A$47</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
     <definedName name="safety">원본!$K$44</definedName>
@@ -673,6 +673,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -682,6 +688,153 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -708,159 +861,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1207,17 +1207,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1229,861 +1229,956 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="44" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="44" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="44"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="44" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="44" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="64" t="s">
+      <c r="J9" s="3"/>
+      <c r="K9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="64"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="56" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56" t="s">
+      <c r="D12" s="16"/>
+      <c r="E12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="44" t="s">
+      <c r="F12" s="16"/>
+      <c r="G12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="44"/>
-      <c r="I12" s="56" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="56"/>
-      <c r="K12" s="44" t="s">
+      <c r="J12" s="16"/>
+      <c r="K12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="44"/>
+      <c r="L12" s="3"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="40" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="57" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="57" t="s">
+      <c r="F16" s="17"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="57"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="15" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="15" t="s">
+      <c r="F18" s="9"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="7"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="48" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="52" t="s">
+      <c r="D21" s="22"/>
+      <c r="E21" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="48" t="s">
+      <c r="F21" s="26"/>
+      <c r="G21" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="49"/>
-      <c r="I21" s="52" t="s">
+      <c r="H21" s="22"/>
+      <c r="I21" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="53"/>
-      <c r="K21" s="56" t="s">
+      <c r="J21" s="26"/>
+      <c r="K21" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="56"/>
+      <c r="L21" s="16"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="56"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45" t="s">
+      <c r="D25" s="30"/>
+      <c r="E25" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46" t="s">
+      <c r="F25" s="30"/>
+      <c r="G25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="46"/>
-      <c r="I25" s="47" t="s">
+      <c r="H25" s="31"/>
+      <c r="I25" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47" t="s">
+      <c r="J25" s="32"/>
+      <c r="K25" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="47"/>
+      <c r="L25" s="32"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="43"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="7"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="35" t="s">
+      <c r="B36" s="36"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="36"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="35" t="s">
+      <c r="F36" s="44"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="J36" s="36"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="26"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="40"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="31"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="28"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="41"/>
+      <c r="L37" s="42"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="29" t="s">
+      <c r="B38" s="36"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="25" t="s">
+      <c r="F38" s="36"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="26"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="40"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="31"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="28"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="42"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="7"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="21" t="s">
+      <c r="B41" s="48"/>
+      <c r="C41" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="17" t="s">
+      <c r="D41" s="52"/>
+      <c r="E41" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="17" t="s">
+      <c r="F41" s="48"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="J41" s="18"/>
-      <c r="K41" s="21" t="s">
+      <c r="J41" s="48"/>
+      <c r="K41" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L41" s="22"/>
+      <c r="L41" s="52"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="24"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="7"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="16" t="s">
+      <c r="B44" s="9"/>
+      <c r="C44" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="15" t="s">
+      <c r="D44" s="20"/>
+      <c r="E44" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="15"/>
-      <c r="G44" s="16" t="s">
+      <c r="F44" s="9"/>
+      <c r="G44" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="H44" s="16"/>
-      <c r="I44" s="15" t="s">
+      <c r="H44" s="20"/>
+      <c r="I44" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J44" s="15"/>
-      <c r="K44" s="16" t="s">
+      <c r="J44" s="9"/>
+      <c r="K44" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="L44" s="16"/>
+      <c r="L44" s="20"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="8"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="58"/>
+      <c r="L47" s="59"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="11"/>
+      <c r="A48" s="60"/>
+      <c r="B48" s="61"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="61"/>
+      <c r="J48" s="61"/>
+      <c r="K48" s="61"/>
+      <c r="L48" s="62"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="11"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="61"/>
+      <c r="C49" s="61"/>
+      <c r="D49" s="61"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="61"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="61"/>
+      <c r="K49" s="61"/>
+      <c r="L49" s="62"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="11"/>
+      <c r="A50" s="60"/>
+      <c r="B50" s="61"/>
+      <c r="C50" s="61"/>
+      <c r="D50" s="61"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="61"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="61"/>
+      <c r="J50" s="61"/>
+      <c r="K50" s="61"/>
+      <c r="L50" s="62"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="61"/>
+      <c r="C51" s="61"/>
+      <c r="D51" s="61"/>
+      <c r="E51" s="61"/>
+      <c r="F51" s="61"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="61"/>
+      <c r="I51" s="61"/>
+      <c r="J51" s="61"/>
+      <c r="K51" s="61"/>
+      <c r="L51" s="62"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="11"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="61"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="61"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="61"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="61"/>
+      <c r="L52" s="62"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="12"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-      <c r="L53" s="14"/>
+      <c r="A53" s="63"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="64"/>
+      <c r="F53" s="64"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="64"/>
+      <c r="I53" s="64"/>
+      <c r="J53" s="64"/>
+      <c r="K53" s="64"/>
+      <c r="L53" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="113">
+    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A47:L53"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A44:B45"/>
+    <mergeCell ref="C44:D45"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:H45"/>
+    <mergeCell ref="I44:J45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="K41:L42"/>
+    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:L39"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:F37"/>
+    <mergeCell ref="G36:H37"/>
+    <mergeCell ref="I36:J37"/>
+    <mergeCell ref="K36:L37"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="K33:L34"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="K31:L32"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="K25:L26"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
     <mergeCell ref="A9:B10"/>
     <mergeCell ref="C9:D10"/>
     <mergeCell ref="E9:F10"/>
@@ -2102,101 +2197,6 @@
     <mergeCell ref="I7:J8"/>
     <mergeCell ref="K7:L8"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="K25:L26"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="K31:L32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:F37"/>
-    <mergeCell ref="G36:H37"/>
-    <mergeCell ref="I36:J37"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K41:L42"/>
-    <mergeCell ref="A38:B39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:L39"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="A47:L53"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A44:B45"/>
-    <mergeCell ref="C44:D45"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:H45"/>
-    <mergeCell ref="I44:J45"/>
-    <mergeCell ref="K44:L45"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/09.Stacking.xlsx
+++ b/src/assets/worklog/09.Stacking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0B3486-ECBE-4A40-BA0F-77739C0B5477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A0ED5A-AD2D-4E8D-9261-8BF46581CFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
+    <workbookView xWindow="1440" yWindow="165" windowWidth="24690" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -23,18 +23,18 @@
     <definedName name="cathodeMagazineLot1">원본!$C$16</definedName>
     <definedName name="cathodeMagazineLot2">원본!$G$16</definedName>
     <definedName name="cathodeMagazineLot3">원본!$K$16</definedName>
-    <definedName name="cleanCheck">원본!$G$44</definedName>
-    <definedName name="equipmentCheckResult">원본!$C$41</definedName>
-    <definedName name="equipmentIssue">원본!$K$41</definedName>
+    <definedName name="cleanCheck">원본!$G$52</definedName>
+    <definedName name="equipmentCheckResult">원본!$C$49</definedName>
+    <definedName name="equipmentIssue">원본!$K$49</definedName>
     <definedName name="hipot1ActualInput">원본!#REF!</definedName>
     <definedName name="hipot1DefectQuantity">원본!#REF!</definedName>
     <definedName name="hipot1DefectRate">원본!#REF!</definedName>
     <definedName name="hipot1DiscardQuantity">원본!#REF!</definedName>
     <definedName name="hipot1GoodQuantity">원본!#REF!</definedName>
-    <definedName name="hipotVoltage">원본!$G$38</definedName>
-    <definedName name="jellyRollThickness">원본!$G$36</definedName>
-    <definedName name="jellyRollWeight">원본!$C$36</definedName>
-    <definedName name="jigNumber">원본!$G$41</definedName>
+    <definedName name="hipotVoltage">원본!$G$46</definedName>
+    <definedName name="jellyRollThickness">원본!$G$44</definedName>
+    <definedName name="jellyRollWeight">원본!$C$44</definedName>
+    <definedName name="jigNumber">원본!$G$49</definedName>
     <definedName name="jr1AnodeLot">원본!$E$27</definedName>
     <definedName name="jr1CathodeLot">원본!$C$27</definedName>
     <definedName name="jr1ElectrodeDefect">원본!$K$27</definedName>
@@ -59,31 +59,55 @@
     <definedName name="jr4Range">원본!$A$33</definedName>
     <definedName name="jr4SeparatorLot">원본!$G$33</definedName>
     <definedName name="jr4WorkTime">원본!$I$33</definedName>
+    <definedName name="jr5AnodeLot">원본!$E$35</definedName>
+    <definedName name="jr5CathodeLot">원본!$C$35</definedName>
+    <definedName name="jr5ElectrodeDefect">원본!$K$35</definedName>
+    <definedName name="jr5Range">원본!$A$35</definedName>
+    <definedName name="jr5SeparatorLot">원본!$G$35</definedName>
+    <definedName name="jr5WorkTime">원본!$I$35</definedName>
+    <definedName name="jr6AnodeLot">원본!$E$37</definedName>
+    <definedName name="jr6CathodeLot">원본!$C$37</definedName>
+    <definedName name="jr6ElectrodeDefect">원본!$K$37</definedName>
+    <definedName name="jr6Range">원본!$A$37</definedName>
+    <definedName name="jr6SeparatorLot">원본!$G$37</definedName>
+    <definedName name="jr6WorkTime">원본!$I$37</definedName>
+    <definedName name="jr7AnodeLot">원본!$E$39</definedName>
+    <definedName name="jr7CathodeLot">원본!$C$39</definedName>
+    <definedName name="jr7ElectrodeDefect">원본!$K$39</definedName>
+    <definedName name="jr7Range">원본!$A$39</definedName>
+    <definedName name="jr7SeparatorLot">원본!$G$39</definedName>
+    <definedName name="jr7WorkTime">원본!$I$39</definedName>
+    <definedName name="jr8AnodeLot">원본!$E$41</definedName>
+    <definedName name="jr8CathodeLot">원본!$C$41</definedName>
+    <definedName name="jr8ElectrodeDefect">원본!$K$41</definedName>
+    <definedName name="jr8Range">원본!$A$41</definedName>
+    <definedName name="jr8SeparatorLot">원본!$G$41</definedName>
+    <definedName name="jr8WorkTime">원본!$I$41</definedName>
     <definedName name="line">원본!$C$9</definedName>
     <definedName name="manufactureDate">원본!$C$7</definedName>
     <definedName name="plant">원본!$G$9</definedName>
     <definedName name="projectId">원본!$G$7</definedName>
-    <definedName name="remark">원본!$A$47</definedName>
+    <definedName name="remark">원본!$A$55</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
-    <definedName name="safety">원본!$K$44</definedName>
+    <definedName name="safety">원본!$K$52</definedName>
     <definedName name="separatorInputQuantity">원본!$I$14</definedName>
     <definedName name="separatorLot">원본!$C$14</definedName>
     <definedName name="separatorManufacturer">원본!$E$14</definedName>
     <definedName name="separatorSpec">원본!$G$14</definedName>
-    <definedName name="separatorTopBottomDimension">원본!$K$36</definedName>
+    <definedName name="separatorTopBottomDimension">원본!$K$44</definedName>
     <definedName name="separatorUsage">원본!$K$14</definedName>
     <definedName name="shift">원본!$K$9</definedName>
     <definedName name="stackActualInput">원본!$C$23</definedName>
-    <definedName name="stackCount">원본!$C$38</definedName>
+    <definedName name="stackCount">원본!$C$46</definedName>
     <definedName name="stackDefectQuantity">원본!$G$23</definedName>
     <definedName name="stackDefectRate">원본!$K$23</definedName>
     <definedName name="stackDiscardQuantity">원본!$I$23</definedName>
     <definedName name="stackGoodQuantity">원본!$E$23</definedName>
-    <definedName name="tempHumi">원본!$C$44</definedName>
+    <definedName name="tempHumi">원본!$C$52</definedName>
     <definedName name="worker">원본!$K$7</definedName>
     <definedName name="writer">원본!$J$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -104,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
   <si>
     <t>스택 작업 일지</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -375,6 +399,18 @@
   <si>
     <t>없음</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>80~100</t>
+  </si>
+  <si>
+    <t>100~120</t>
+  </si>
+  <si>
+    <t>120~140</t>
+  </si>
+  <si>
+    <t>140~160</t>
   </si>
 </sst>
 </file>
@@ -673,12 +709,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -688,10 +718,166 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -700,167 +886,17 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1195,29 +1231,51 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="550" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C1147BB6-6C77-467D-B5CF-49A4038EF34C}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="ko-KR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="ko-KR" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;2930134a-71ee-4c66-985b-c64c50b1038b&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE5B212-3A04-48A6-B951-590525EA0B74}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="10" max="12" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1229,956 +1287,994 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="7"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="3" t="s">
+      <c r="F7" s="44"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="3" t="s">
+      <c r="F9" s="44"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4" t="s">
+      <c r="J9" s="44"/>
+      <c r="K9" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="4"/>
+      <c r="L9" s="64"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16" t="s">
+      <c r="D12" s="56"/>
+      <c r="E12" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="3" t="s">
+      <c r="F12" s="56"/>
+      <c r="G12" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="16" t="s">
+      <c r="H12" s="44"/>
+      <c r="I12" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="3" t="s">
+      <c r="J12" s="56"/>
+      <c r="K12" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="44"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="14" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17" t="s">
+      <c r="B16" s="57"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="17" t="s">
+      <c r="F16" s="57"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="59"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="9" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="9" t="s">
+      <c r="F18" s="15"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="7"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="21" t="s">
+      <c r="B21" s="44"/>
+      <c r="C21" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="25" t="s">
+      <c r="D21" s="49"/>
+      <c r="E21" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="21" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="22"/>
-      <c r="I21" s="25" t="s">
+      <c r="H21" s="49"/>
+      <c r="I21" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="16" t="s">
+      <c r="J21" s="53"/>
+      <c r="K21" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="16"/>
+      <c r="L21" s="56"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="30" t="s">
+      <c r="B25" s="44"/>
+      <c r="C25" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30" t="s">
+      <c r="D25" s="45"/>
+      <c r="E25" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31" t="s">
+      <c r="F25" s="45"/>
+      <c r="G25" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="31"/>
-      <c r="I25" s="32" t="s">
+      <c r="H25" s="46"/>
+      <c r="I25" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32" t="s">
+      <c r="J25" s="47"/>
+      <c r="K25" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="32"/>
+      <c r="L25" s="47"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="43"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="41"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="41"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="41"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
+      <c r="L42" s="41"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="7"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="35" t="s">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="43" t="s">
+      <c r="B44" s="30"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="44"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="43" t="s">
+      <c r="F44" s="36"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="J36" s="44"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="40"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="42"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="35" t="s">
+      <c r="J44" s="36"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="26"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="31"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="27"/>
+      <c r="L45" s="28"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="35" t="s">
+      <c r="B46" s="30"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="F38" s="36"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="39" t="s">
+      <c r="F46" s="30"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="40"/>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="42"/>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="5" t="s">
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="26"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="31"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="28"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="7"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="47" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="51" t="s">
+      <c r="B49" s="18"/>
+      <c r="C49" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="47" t="s">
+      <c r="D49" s="22"/>
+      <c r="E49" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="48"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="47" t="s">
+      <c r="F49" s="18"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J41" s="48"/>
-      <c r="K41" s="51" t="s">
+      <c r="J49" s="18"/>
+      <c r="K49" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="L41" s="52"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="49"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="54"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="5" t="s">
+      <c r="L49" s="22"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="19"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="24"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="7"/>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="9" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="20" t="s">
+      <c r="B52" s="15"/>
+      <c r="C52" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="9" t="s">
+      <c r="D52" s="16"/>
+      <c r="E52" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="20" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="H44" s="20"/>
-      <c r="I44" s="9" t="s">
+      <c r="H52" s="16"/>
+      <c r="I52" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J44" s="9"/>
-      <c r="K44" s="20" t="s">
+      <c r="J52" s="15"/>
+      <c r="K52" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L44" s="20"/>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="5" t="s">
+      <c r="L52" s="16"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="57" t="s">
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="58"/>
-      <c r="K47" s="58"/>
-      <c r="L47" s="59"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="60"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="61"/>
-      <c r="J48" s="61"/>
-      <c r="K48" s="61"/>
-      <c r="L48" s="62"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="60"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="61"/>
-      <c r="K49" s="61"/>
-      <c r="L49" s="62"/>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="60"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61"/>
-      <c r="J50" s="61"/>
-      <c r="K50" s="61"/>
-      <c r="L50" s="62"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="60"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="61"/>
-      <c r="J51" s="61"/>
-      <c r="K51" s="61"/>
-      <c r="L51" s="62"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="60"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
-      <c r="L52" s="62"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="63"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="64"/>
-      <c r="E53" s="64"/>
-      <c r="F53" s="64"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="64"/>
-      <c r="I53" s="64"/>
-      <c r="J53" s="64"/>
-      <c r="K53" s="64"/>
-      <c r="L53" s="65"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="8"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="11"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="11"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="11"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="11"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="11"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="A47:L53"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A44:B45"/>
-    <mergeCell ref="C44:D45"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:H45"/>
-    <mergeCell ref="I44:J45"/>
-    <mergeCell ref="K44:L45"/>
+  <mergeCells count="137">
+    <mergeCell ref="K37:L38"/>
+    <mergeCell ref="A39:B40"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
     <mergeCell ref="A41:B42"/>
     <mergeCell ref="C41:D42"/>
     <mergeCell ref="E41:F42"/>
     <mergeCell ref="G41:H42"/>
     <mergeCell ref="I41:J42"/>
     <mergeCell ref="K41:L42"/>
-    <mergeCell ref="A38:B39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:L39"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:F37"/>
-    <mergeCell ref="G36:H37"/>
-    <mergeCell ref="I36:J37"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="K31:L32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="K25:L26"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
     <mergeCell ref="A9:B10"/>
     <mergeCell ref="C9:D10"/>
     <mergeCell ref="E9:F10"/>
@@ -2197,9 +2293,115 @@
     <mergeCell ref="I7:J8"/>
     <mergeCell ref="K7:L8"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="K25:L26"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="K31:L32"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A44:B45"/>
+    <mergeCell ref="C44:D45"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:H45"/>
+    <mergeCell ref="I44:J45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="K33:L34"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="K35:L36"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="G37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="A49:B50"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="I46:L47"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A55:L61"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:B53"/>
+    <mergeCell ref="C52:D53"/>
+    <mergeCell ref="E52:F53"/>
+    <mergeCell ref="G52:H53"/>
+    <mergeCell ref="I52:J53"/>
+    <mergeCell ref="K52:L53"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="74" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/assets/worklog/09.Stacking.xlsx
+++ b/src/assets/worklog/09.Stacking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A0ED5A-AD2D-4E8D-9261-8BF46581CFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E309DFC-157B-46B8-9F80-57EA1017D8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="165" windowWidth="24690" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -35,51 +35,59 @@
     <definedName name="jellyRollThickness">원본!$G$44</definedName>
     <definedName name="jellyRollWeight">원본!$C$44</definedName>
     <definedName name="jigNumber">원본!$G$49</definedName>
+    <definedName name="jr1AnodeDefect">원본!$L$27</definedName>
     <definedName name="jr1AnodeLot">원본!$E$27</definedName>
+    <definedName name="jr1CathodeDefect">원본!$K$27</definedName>
     <definedName name="jr1CathodeLot">원본!$C$27</definedName>
-    <definedName name="jr1ElectrodeDefect">원본!$K$27</definedName>
     <definedName name="jr1Range">원본!$A$27</definedName>
     <definedName name="jr1SeparatorLot">원본!$G$27</definedName>
     <definedName name="jr1WorkTime">원본!$I$27</definedName>
+    <definedName name="jr2AnodeDefect">원본!$L$29</definedName>
     <definedName name="jr2AnodeLot">원본!$E$29</definedName>
+    <definedName name="jr2CathodeDefect">원본!$K$29</definedName>
     <definedName name="jr2CathodeLot">원본!$C$29</definedName>
-    <definedName name="jr2ElectrodeDefect">원본!$K$29</definedName>
     <definedName name="jr2Range">원본!$A$29</definedName>
     <definedName name="jr2SeparatorLot">원본!$G$29</definedName>
     <definedName name="jr2WorkTime">원본!$I$29</definedName>
+    <definedName name="jr3AnodeDefect">원본!$L$31</definedName>
     <definedName name="jr3AnodeLot">원본!$E$31</definedName>
+    <definedName name="jr3CathodeDefect">원본!$K$31</definedName>
     <definedName name="jr3CathodeLot">원본!$C$31</definedName>
-    <definedName name="jr3ElectrodeDefect">원본!$K$31</definedName>
     <definedName name="jr3Range">원본!$A$31</definedName>
     <definedName name="jr3SeparatorLot">원본!$G$31</definedName>
     <definedName name="jr3WorkTime">원본!$I$31</definedName>
+    <definedName name="jr4AnodeDefect">원본!$L$33</definedName>
     <definedName name="jr4AnodeLot">원본!$E$33</definedName>
+    <definedName name="jr4CathodeDefect">원본!$K$33</definedName>
     <definedName name="jr4CathodeLot">원본!$C$33</definedName>
-    <definedName name="jr4ElectrodeDefect">원본!$K$33</definedName>
     <definedName name="jr4Range">원본!$A$33</definedName>
     <definedName name="jr4SeparatorLot">원본!$G$33</definedName>
     <definedName name="jr4WorkTime">원본!$I$33</definedName>
+    <definedName name="jr5AnodeDefect">원본!$L$35</definedName>
     <definedName name="jr5AnodeLot">원본!$E$35</definedName>
+    <definedName name="jr5CathodeDefect">원본!$K$35</definedName>
     <definedName name="jr5CathodeLot">원본!$C$35</definedName>
-    <definedName name="jr5ElectrodeDefect">원본!$K$35</definedName>
     <definedName name="jr5Range">원본!$A$35</definedName>
     <definedName name="jr5SeparatorLot">원본!$G$35</definedName>
     <definedName name="jr5WorkTime">원본!$I$35</definedName>
+    <definedName name="jr6AnodeDefect">원본!$L$37</definedName>
     <definedName name="jr6AnodeLot">원본!$E$37</definedName>
+    <definedName name="jr6CathodeDefect">원본!$K$37</definedName>
     <definedName name="jr6CathodeLot">원본!$C$37</definedName>
-    <definedName name="jr6ElectrodeDefect">원본!$K$37</definedName>
     <definedName name="jr6Range">원본!$A$37</definedName>
     <definedName name="jr6SeparatorLot">원본!$G$37</definedName>
     <definedName name="jr6WorkTime">원본!$I$37</definedName>
+    <definedName name="jr7AnodeDefect">원본!$L$39</definedName>
     <definedName name="jr7AnodeLot">원본!$E$39</definedName>
+    <definedName name="jr7CathodeDefect">원본!$K$39</definedName>
     <definedName name="jr7CathodeLot">원본!$C$39</definedName>
-    <definedName name="jr7ElectrodeDefect">원본!$K$39</definedName>
     <definedName name="jr7Range">원본!$A$39</definedName>
     <definedName name="jr7SeparatorLot">원본!$G$39</definedName>
     <definedName name="jr7WorkTime">원본!$I$39</definedName>
+    <definedName name="jr8AnodeDefect">원본!$L$41</definedName>
     <definedName name="jr8AnodeLot">원본!$E$41</definedName>
+    <definedName name="jr8CathodeDefect">원본!$K$41</definedName>
     <definedName name="jr8CathodeLot">원본!$C$41</definedName>
-    <definedName name="jr8ElectrodeDefect">원본!$K$41</definedName>
     <definedName name="jr8Range">원본!$A$41</definedName>
     <definedName name="jr8SeparatorLot">원본!$G$41</definedName>
     <definedName name="jr8WorkTime">원본!$I$41</definedName>
@@ -128,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>스택 작업 일지</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -283,10 +291,6 @@
   </si>
   <si>
     <t>작업 시간(시작/종료)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>전극 파손(EA)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -411,6 +415,12 @@
   </si>
   <si>
     <t>140~160</t>
+  </si>
+  <si>
+    <t>전극 파손 (양극)</t>
+  </si>
+  <si>
+    <t>전극 파손 (음극)</t>
   </si>
 </sst>
 </file>
@@ -421,7 +431,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,8 +511,17 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,8 +540,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -690,6 +715,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -699,7 +737,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -709,6 +747,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -718,6 +774,138 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -745,158 +933,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1233,7 +1286,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="550" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="730" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1261,21 +1314,22 @@
   <dimension ref="A1:L61"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="10" max="12" width="9" style="2"/>
+    <col min="10" max="11" width="9" style="2"/>
+    <col min="12" max="12" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1287,994 +1341,1097 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="11"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="44" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="44" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="44"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="44" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="44" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="64" t="s">
+      <c r="J9" s="7"/>
+      <c r="K9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="64"/>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="11"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="56" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="44" t="s">
+      <c r="F12" s="17"/>
+      <c r="G12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="44"/>
-      <c r="I12" s="56" t="s">
+      <c r="H12" s="7"/>
+      <c r="I12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="56"/>
-      <c r="K12" s="44" t="s">
+      <c r="J12" s="17"/>
+      <c r="K12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="44"/>
+      <c r="L12" s="7"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="40" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="57" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="57" t="s">
+      <c r="F16" s="18"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="57"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="15" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="15" t="s">
+      <c r="F18" s="3"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="5"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="11"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="48" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="52" t="s">
+      <c r="D21" s="23"/>
+      <c r="E21" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="48" t="s">
+      <c r="F21" s="27"/>
+      <c r="G21" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="49"/>
-      <c r="I21" s="52" t="s">
+      <c r="H21" s="23"/>
+      <c r="I21" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="53"/>
-      <c r="K21" s="56" t="s">
+      <c r="J21" s="27"/>
+      <c r="K21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="56"/>
+      <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="56"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45" t="s">
+      <c r="D25" s="30"/>
+      <c r="E25" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46" t="s">
+      <c r="F25" s="30"/>
+      <c r="G25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="46"/>
-      <c r="I25" s="47" t="s">
+      <c r="H25" s="31"/>
+      <c r="I25" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47" t="s">
+      <c r="J25" s="32"/>
+      <c r="K25" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="66"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="47"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="15" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="15" t="s">
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="43"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="15" t="s">
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="68"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="15" t="s">
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="67"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="68"/>
+      <c r="L34" s="68"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="68"/>
+      <c r="L36" s="68"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="68"/>
+      <c r="L38" s="68"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="67"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="68"/>
+      <c r="L40" s="68"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="68"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="43"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="43"/>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="41"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="3" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="5"/>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="29" t="s">
+      <c r="B44" s="35"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="35" t="s">
+      <c r="F44" s="43"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="F44" s="36"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="35" t="s">
+      <c r="J44" s="43"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="39"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="41"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="J44" s="36"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="26"/>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="31"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="28"/>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="29" t="s">
+      <c r="B46" s="35"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="29" t="s">
+      <c r="F46" s="35"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="39"/>
+      <c r="I46" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F46" s="30"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="25" t="s">
+      <c r="J46" s="54"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="39"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="36"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="55"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="41"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="26"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="31"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="28"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="3" t="s">
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="17" t="s">
+      <c r="B49" s="47"/>
+      <c r="C49" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="51"/>
+      <c r="E49" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="18"/>
-      <c r="C49" s="21" t="s">
+      <c r="F49" s="47"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="J49" s="47"/>
+      <c r="K49" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="L49" s="51"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="48"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="48"/>
+      <c r="J50" s="49"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="53"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="11"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="21"/>
+      <c r="E52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="21"/>
+      <c r="I52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="22"/>
-      <c r="E49" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" s="18"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J49" s="18"/>
-      <c r="K49" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="L49" s="22"/>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="19"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="23"/>
-      <c r="L50" s="24"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D52" s="16"/>
-      <c r="E52" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="H52" s="16"/>
-      <c r="I52" s="15" t="s">
+      <c r="L52" s="21"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J52" s="15"/>
-      <c r="K52" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L52" s="16"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="15"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="3" t="s">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="11"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="8"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="58"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="9"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="11"/>
+      <c r="A56" s="59"/>
+      <c r="B56" s="60"/>
+      <c r="C56" s="60"/>
+      <c r="D56" s="60"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="60"/>
+      <c r="G56" s="60"/>
+      <c r="H56" s="60"/>
+      <c r="I56" s="60"/>
+      <c r="J56" s="60"/>
+      <c r="K56" s="60"/>
+      <c r="L56" s="61"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="9"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="11"/>
+      <c r="A57" s="59"/>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
+      <c r="H57" s="60"/>
+      <c r="I57" s="60"/>
+      <c r="J57" s="60"/>
+      <c r="K57" s="60"/>
+      <c r="L57" s="61"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="9"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="11"/>
+      <c r="A58" s="59"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="60"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="60"/>
+      <c r="J58" s="60"/>
+      <c r="K58" s="60"/>
+      <c r="L58" s="61"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="9"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="11"/>
+      <c r="A59" s="59"/>
+      <c r="B59" s="60"/>
+      <c r="C59" s="60"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="60"/>
+      <c r="F59" s="60"/>
+      <c r="G59" s="60"/>
+      <c r="H59" s="60"/>
+      <c r="I59" s="60"/>
+      <c r="J59" s="60"/>
+      <c r="K59" s="60"/>
+      <c r="L59" s="61"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="9"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="11"/>
+      <c r="A60" s="59"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="60"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="60"/>
+      <c r="G60" s="60"/>
+      <c r="H60" s="60"/>
+      <c r="I60" s="60"/>
+      <c r="J60" s="60"/>
+      <c r="K60" s="60"/>
+      <c r="L60" s="61"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
-      <c r="L61" s="14"/>
+      <c r="A61" s="62"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="63"/>
+      <c r="J61" s="63"/>
+      <c r="K61" s="63"/>
+      <c r="L61" s="64"/>
     </row>
   </sheetData>
-  <mergeCells count="137">
-    <mergeCell ref="K37:L38"/>
-    <mergeCell ref="A39:B40"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K41:L42"/>
+  <mergeCells count="146">
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A55:L61"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:B53"/>
+    <mergeCell ref="C52:D53"/>
+    <mergeCell ref="E52:F53"/>
+    <mergeCell ref="G52:H53"/>
+    <mergeCell ref="I52:J53"/>
+    <mergeCell ref="K52:L53"/>
+    <mergeCell ref="A49:B50"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="I46:L47"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A44:B45"/>
+    <mergeCell ref="C44:D45"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:H45"/>
+    <mergeCell ref="I44:J45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="G37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
     <mergeCell ref="A9:B10"/>
     <mergeCell ref="C9:D10"/>
     <mergeCell ref="E9:F10"/>
@@ -2293,112 +2450,20 @@
     <mergeCell ref="I7:J8"/>
     <mergeCell ref="K7:L8"/>
     <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="K25:L26"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="K31:L32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A44:B45"/>
-    <mergeCell ref="C44:D45"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:H45"/>
-    <mergeCell ref="I44:J45"/>
-    <mergeCell ref="K44:L45"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
-    <mergeCell ref="K35:L36"/>
-    <mergeCell ref="A37:B38"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:F38"/>
-    <mergeCell ref="G37:H38"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="A49:B50"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D47"/>
-    <mergeCell ref="E46:F47"/>
-    <mergeCell ref="G46:H47"/>
-    <mergeCell ref="I46:L47"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A54:L54"/>
-    <mergeCell ref="A55:L61"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:B53"/>
-    <mergeCell ref="C52:D53"/>
-    <mergeCell ref="E52:F53"/>
-    <mergeCell ref="G52:H53"/>
-    <mergeCell ref="I52:J53"/>
-    <mergeCell ref="K52:L53"/>
+    <mergeCell ref="A39:B40"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="L41:L42"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/09.Stacking.xlsx
+++ b/src/assets/worklog/09.Stacking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E309DFC-157B-46B8-9F80-57EA1017D8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6CD42F-D199-4D53-A2D9-2ABCFE5855C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
+    <workbookView xWindow="1320" yWindow="330" windowWidth="25290" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -747,22 +747,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
@@ -774,7 +762,169 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -789,167 +939,17 @@
     <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1319,17 +1319,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1341,1014 +1341,1074 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="7" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="7" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="7" t="s">
+      <c r="B9" s="43"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="7" t="s">
+      <c r="F9" s="43"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="43"/>
+      <c r="K9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="8"/>
+      <c r="L9" s="67"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="7"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="59"/>
+      <c r="E12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="59"/>
+      <c r="G12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="17" t="s">
+      <c r="H12" s="43"/>
+      <c r="I12" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="7" t="s">
+      <c r="J12" s="59"/>
+      <c r="K12" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="7"/>
+      <c r="L12" s="43"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="5" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="18" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="18" t="s">
+      <c r="F16" s="60"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="62"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="3" t="s">
+      <c r="B18" s="17"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="3" t="s">
+      <c r="F18" s="17"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="11"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="7"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="22" t="s">
+      <c r="B21" s="43"/>
+      <c r="C21" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="26" t="s">
+      <c r="D21" s="52"/>
+      <c r="E21" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="56"/>
+      <c r="G21" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="26" t="s">
+      <c r="H21" s="52"/>
+      <c r="I21" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="17" t="s">
+      <c r="J21" s="56"/>
+      <c r="K21" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="17"/>
+      <c r="L21" s="59"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="30" t="s">
+      <c r="B25" s="43"/>
+      <c r="C25" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30" t="s">
+      <c r="D25" s="44"/>
+      <c r="E25" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="31" t="s">
+      <c r="F25" s="44"/>
+      <c r="G25" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="31"/>
-      <c r="I25" s="32" t="s">
+      <c r="H25" s="45"/>
+      <c r="I25" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="32"/>
-      <c r="K25" s="69" t="s">
+      <c r="J25" s="46"/>
+      <c r="K25" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="L25" s="65" t="s">
+      <c r="L25" s="49" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="66"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="68"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="67"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="68"/>
-      <c r="L32" s="68"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="67"/>
-      <c r="L33" s="67"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="68"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="67"/>
-      <c r="L35" s="67"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="68"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="67"/>
-      <c r="L37" s="67"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="68"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="11"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="7"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="34" t="s">
+      <c r="A44" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="35"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="42" t="s">
+      <c r="B44" s="32"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="43"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="42" t="s">
+      <c r="F44" s="38"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="J44" s="43"/>
-      <c r="K44" s="38"/>
-      <c r="L44" s="39"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="28"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="36"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="41"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="30"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="35"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="34" t="s">
+      <c r="B46" s="32"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F46" s="35"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="38" t="s">
+      <c r="F46" s="32"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="J46" s="54"/>
-      <c r="K46" s="54"/>
-      <c r="L46" s="39"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="28"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="36"/>
-      <c r="B47" s="37"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="55"/>
-      <c r="K47" s="55"/>
-      <c r="L47" s="41"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="30"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="11"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="50" t="s">
+      <c r="B49" s="20"/>
+      <c r="C49" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="51"/>
-      <c r="E49" s="46" t="s">
+      <c r="D49" s="24"/>
+      <c r="E49" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F49" s="47"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="46" t="s">
+      <c r="F49" s="20"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J49" s="47"/>
-      <c r="K49" s="50" t="s">
+      <c r="J49" s="20"/>
+      <c r="K49" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="L49" s="51"/>
+      <c r="L49" s="24"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="48"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="49"/>
-      <c r="K50" s="52"/>
-      <c r="L50" s="53"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="26"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="7"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="21" t="s">
+      <c r="B52" s="17"/>
+      <c r="C52" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="3" t="s">
+      <c r="D52" s="18"/>
+      <c r="E52" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="21" t="s">
+      <c r="F52" s="17"/>
+      <c r="G52" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H52" s="21"/>
-      <c r="I52" s="3" t="s">
+      <c r="H52" s="18"/>
+      <c r="I52" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="21" t="s">
+      <c r="J52" s="17"/>
+      <c r="K52" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="L52" s="21"/>
+      <c r="L52" s="18"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="21"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="11"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="56" t="s">
+      <c r="A55" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="57"/>
-      <c r="C55" s="57"/>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
-      <c r="K55" s="57"/>
-      <c r="L55" s="58"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="10"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="59"/>
-      <c r="B56" s="60"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="60"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="60"/>
-      <c r="G56" s="60"/>
-      <c r="H56" s="60"/>
-      <c r="I56" s="60"/>
-      <c r="J56" s="60"/>
-      <c r="K56" s="60"/>
-      <c r="L56" s="61"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="13"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="59"/>
-      <c r="B57" s="60"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="60"/>
-      <c r="E57" s="60"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="60"/>
-      <c r="H57" s="60"/>
-      <c r="I57" s="60"/>
-      <c r="J57" s="60"/>
-      <c r="K57" s="60"/>
-      <c r="L57" s="61"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="13"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="59"/>
-      <c r="B58" s="60"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="60"/>
-      <c r="J58" s="60"/>
-      <c r="K58" s="60"/>
-      <c r="L58" s="61"/>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="13"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="59"/>
-      <c r="B59" s="60"/>
-      <c r="C59" s="60"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="60"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="60"/>
-      <c r="J59" s="60"/>
-      <c r="K59" s="60"/>
-      <c r="L59" s="61"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="13"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="59"/>
-      <c r="B60" s="60"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="60"/>
-      <c r="E60" s="60"/>
-      <c r="F60" s="60"/>
-      <c r="G60" s="60"/>
-      <c r="H60" s="60"/>
-      <c r="I60" s="60"/>
-      <c r="J60" s="60"/>
-      <c r="K60" s="60"/>
-      <c r="L60" s="61"/>
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="13"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="62"/>
-      <c r="B61" s="63"/>
-      <c r="C61" s="63"/>
-      <c r="D61" s="63"/>
-      <c r="E61" s="63"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="63"/>
-      <c r="H61" s="63"/>
-      <c r="I61" s="63"/>
-      <c r="J61" s="63"/>
-      <c r="K61" s="63"/>
-      <c r="L61" s="64"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="146">
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="L33:L34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L35:L36"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="A54:L54"/>
-    <mergeCell ref="A55:L61"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:B53"/>
-    <mergeCell ref="C52:D53"/>
-    <mergeCell ref="E52:F53"/>
-    <mergeCell ref="G52:H53"/>
-    <mergeCell ref="I52:J53"/>
-    <mergeCell ref="K52:L53"/>
-    <mergeCell ref="A49:B50"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D47"/>
-    <mergeCell ref="E46:F47"/>
-    <mergeCell ref="G46:H47"/>
-    <mergeCell ref="I46:L47"/>
-    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A44:B45"/>
     <mergeCell ref="C44:D45"/>
@@ -2371,99 +2431,39 @@
     <mergeCell ref="E37:F38"/>
     <mergeCell ref="G37:H38"/>
     <mergeCell ref="I37:J38"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="K27:K28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A39:B40"/>
     <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="A49:B50"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="I46:L47"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A55:L61"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:B53"/>
+    <mergeCell ref="C52:D53"/>
+    <mergeCell ref="E52:F53"/>
+    <mergeCell ref="G52:H53"/>
+    <mergeCell ref="I52:J53"/>
+    <mergeCell ref="K52:L53"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="K31:K32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="K35:K36"/>
+    <mergeCell ref="L35:L36"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="L37:L38"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/09.Stacking.xlsx
+++ b/src/assets/worklog/09.Stacking.xlsx
@@ -8,21 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6CD42F-D199-4D53-A2D9-2ABCFE5855C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD805008-2FA6-455E-B93E-8D6F600E5E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="330" windowWidth="25290" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
+    <workbookView xWindow="1710" yWindow="195" windowWidth="25260" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="anodeDefect">원본!$L$27</definedName>
     <definedName name="anodeMagazineLot1">원본!$C$18</definedName>
     <definedName name="anodeMagazineLot2">원본!$G$18</definedName>
     <definedName name="anodeMagazineLot3">원본!$K$18</definedName>
+    <definedName name="anodeThickness">원본!$L$46</definedName>
     <definedName name="approver">원본!$L$5</definedName>
+    <definedName name="cathodeDefect">원본!$K$27</definedName>
     <definedName name="cathodeMagazineLot1">원본!$C$16</definedName>
     <definedName name="cathodeMagazineLot2">원본!$G$16</definedName>
     <definedName name="cathodeMagazineLot3">원본!$K$16</definedName>
+    <definedName name="cathodeThickness">원본!$K$46</definedName>
     <definedName name="cleanCheck">원본!$G$52</definedName>
     <definedName name="equipmentCheckResult">원본!$C$49</definedName>
     <definedName name="equipmentIssue">원본!$K$49</definedName>
@@ -35,58 +39,42 @@
     <definedName name="jellyRollThickness">원본!$G$44</definedName>
     <definedName name="jellyRollWeight">원본!$C$44</definedName>
     <definedName name="jigNumber">원본!$G$49</definedName>
-    <definedName name="jr1AnodeDefect">원본!$L$27</definedName>
     <definedName name="jr1AnodeLot">원본!$E$27</definedName>
-    <definedName name="jr1CathodeDefect">원본!$K$27</definedName>
     <definedName name="jr1CathodeLot">원본!$C$27</definedName>
     <definedName name="jr1Range">원본!$A$27</definedName>
     <definedName name="jr1SeparatorLot">원본!$G$27</definedName>
     <definedName name="jr1WorkTime">원본!$I$27</definedName>
-    <definedName name="jr2AnodeDefect">원본!$L$29</definedName>
     <definedName name="jr2AnodeLot">원본!$E$29</definedName>
-    <definedName name="jr2CathodeDefect">원본!$K$29</definedName>
     <definedName name="jr2CathodeLot">원본!$C$29</definedName>
     <definedName name="jr2Range">원본!$A$29</definedName>
     <definedName name="jr2SeparatorLot">원본!$G$29</definedName>
     <definedName name="jr2WorkTime">원본!$I$29</definedName>
-    <definedName name="jr3AnodeDefect">원본!$L$31</definedName>
     <definedName name="jr3AnodeLot">원본!$E$31</definedName>
-    <definedName name="jr3CathodeDefect">원본!$K$31</definedName>
     <definedName name="jr3CathodeLot">원본!$C$31</definedName>
     <definedName name="jr3Range">원본!$A$31</definedName>
     <definedName name="jr3SeparatorLot">원본!$G$31</definedName>
     <definedName name="jr3WorkTime">원본!$I$31</definedName>
-    <definedName name="jr4AnodeDefect">원본!$L$33</definedName>
     <definedName name="jr4AnodeLot">원본!$E$33</definedName>
-    <definedName name="jr4CathodeDefect">원본!$K$33</definedName>
     <definedName name="jr4CathodeLot">원본!$C$33</definedName>
     <definedName name="jr4Range">원본!$A$33</definedName>
     <definedName name="jr4SeparatorLot">원본!$G$33</definedName>
     <definedName name="jr4WorkTime">원본!$I$33</definedName>
-    <definedName name="jr5AnodeDefect">원본!$L$35</definedName>
     <definedName name="jr5AnodeLot">원본!$E$35</definedName>
-    <definedName name="jr5CathodeDefect">원본!$K$35</definedName>
     <definedName name="jr5CathodeLot">원본!$C$35</definedName>
     <definedName name="jr5Range">원본!$A$35</definedName>
     <definedName name="jr5SeparatorLot">원본!$G$35</definedName>
     <definedName name="jr5WorkTime">원본!$I$35</definedName>
-    <definedName name="jr6AnodeDefect">원본!$L$37</definedName>
     <definedName name="jr6AnodeLot">원본!$E$37</definedName>
-    <definedName name="jr6CathodeDefect">원본!$K$37</definedName>
     <definedName name="jr6CathodeLot">원본!$C$37</definedName>
     <definedName name="jr6Range">원본!$A$37</definedName>
     <definedName name="jr6SeparatorLot">원본!$G$37</definedName>
     <definedName name="jr6WorkTime">원본!$I$37</definedName>
-    <definedName name="jr7AnodeDefect">원본!$L$39</definedName>
     <definedName name="jr7AnodeLot">원본!$E$39</definedName>
-    <definedName name="jr7CathodeDefect">원본!$K$39</definedName>
     <definedName name="jr7CathodeLot">원본!$C$39</definedName>
     <definedName name="jr7Range">원본!$A$39</definedName>
     <definedName name="jr7SeparatorLot">원본!$G$39</definedName>
     <definedName name="jr7WorkTime">원본!$I$39</definedName>
-    <definedName name="jr8AnodeDefect">원본!$L$41</definedName>
     <definedName name="jr8AnodeLot">원본!$E$41</definedName>
-    <definedName name="jr8CathodeDefect">원본!$K$41</definedName>
     <definedName name="jr8CathodeLot">원본!$C$41</definedName>
     <definedName name="jr8Range">원본!$A$41</definedName>
     <definedName name="jr8SeparatorLot">원본!$G$41</definedName>
@@ -339,10 +327,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>5. 설비 정보</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -421,6 +405,10 @@
   </si>
   <si>
     <t>전극 파손 (음극)</t>
+  </si>
+  <si>
+    <t>양/음극 두께
+(㎛)</t>
   </si>
 </sst>
 </file>
@@ -491,14 +479,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -517,6 +497,14 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -547,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -728,6 +716,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -737,7 +736,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -747,10 +746,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
@@ -762,6 +776,153 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -789,166 +950,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1286,7 +1312,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="730" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="519" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1319,17 +1345,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1341,1074 +1367,1008 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="68"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="7"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="43" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="43" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="43"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="43" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="43" t="s">
+      <c r="F9" s="9"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="43"/>
-      <c r="K9" s="67" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="67"/>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="43"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="12"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="59" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="43" t="s">
+      <c r="F12" s="13"/>
+      <c r="G12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="43"/>
-      <c r="I12" s="59" t="s">
+      <c r="H12" s="9"/>
+      <c r="I12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="59"/>
-      <c r="K12" s="43" t="s">
+      <c r="J12" s="13"/>
+      <c r="K12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="43"/>
+      <c r="L12" s="9"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="43"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="42" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A15" s="63"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="60" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="60" t="s">
+      <c r="F16" s="14"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="60"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="62"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="17" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="17" t="s">
+      <c r="F18" s="3"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="7"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="12"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="51" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="52"/>
-      <c r="E21" s="55" t="s">
+      <c r="D21" s="22"/>
+      <c r="E21" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="56"/>
-      <c r="G21" s="51" t="s">
+      <c r="F21" s="26"/>
+      <c r="G21" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="52"/>
-      <c r="I21" s="55" t="s">
+      <c r="H21" s="22"/>
+      <c r="I21" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="56"/>
-      <c r="K21" s="59" t="s">
+      <c r="J21" s="26"/>
+      <c r="K21" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="59"/>
+      <c r="L21" s="13"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44" t="s">
+      <c r="D25" s="32"/>
+      <c r="E25" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="44"/>
-      <c r="G25" s="45" t="s">
+      <c r="F25" s="32"/>
+      <c r="G25" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="45"/>
-      <c r="I25" s="46" t="s">
+      <c r="H25" s="33"/>
+      <c r="I25" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="46"/>
-      <c r="K25" s="47" t="s">
+      <c r="J25" s="34"/>
+      <c r="K25" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="L25" s="49" t="s">
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="73"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="77"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="78"/>
+      <c r="L28" s="78"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="78"/>
+      <c r="L29" s="78"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="78"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="78"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="78"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="78"/>
+      <c r="L33" s="78"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="78"/>
+      <c r="L34" s="78"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="78"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="78"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="78"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="78"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="78"/>
+      <c r="L39" s="78"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="78"/>
+      <c r="L40" s="78"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="78"/>
+      <c r="L41" s="78"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="71"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="79"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="76"/>
+    </row>
+    <row r="44" spans="1:12" ht="16.5" customHeight="1">
+      <c r="A44" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="37"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="45"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="48"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="41"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="38"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="43"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="37"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="37"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="59" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="43"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="50"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="69"/>
-      <c r="J33" s="69"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-    </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="69"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="7"/>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" s="38"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" s="38"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="28"/>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="33"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="40"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="30"/>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="32"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="32"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="27" t="s">
+      <c r="J46" s="48"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="38"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="61"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="28"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="33"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="30"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" s="5" t="s">
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="12"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="7"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="19" t="s">
+      <c r="B49" s="52"/>
+      <c r="C49" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" s="56"/>
+      <c r="E49" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="23" t="s">
+      <c r="F49" s="52"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="J49" s="52"/>
+      <c r="K49" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="L49" s="56"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="53"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="57"/>
+      <c r="L50" s="58"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="12"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="31"/>
+      <c r="E52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H52" s="31"/>
+      <c r="I52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="J49" s="20"/>
-      <c r="K49" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="L49" s="24"/>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="21"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="25"/>
-      <c r="L50" s="26"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="7"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="17"/>
-      <c r="G52" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="H52" s="18"/>
-      <c r="I52" s="17" t="s">
+      <c r="L52" s="31"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J52" s="17"/>
-      <c r="K52" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="L52" s="18"/>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54" s="5" t="s">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="7"/>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="10"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="64"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="12"/>
-      <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="13"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="66"/>
+      <c r="K56" s="66"/>
+      <c r="L56" s="67"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="13"/>
+      <c r="A57" s="65"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="66"/>
+      <c r="I57" s="66"/>
+      <c r="J57" s="66"/>
+      <c r="K57" s="66"/>
+      <c r="L57" s="67"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="12"/>
-      <c r="J58" s="12"/>
-      <c r="K58" s="12"/>
-      <c r="L58" s="13"/>
+      <c r="A58" s="65"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="66"/>
+      <c r="H58" s="66"/>
+      <c r="I58" s="66"/>
+      <c r="J58" s="66"/>
+      <c r="K58" s="66"/>
+      <c r="L58" s="67"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12"/>
-      <c r="L59" s="13"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="66"/>
+      <c r="K59" s="66"/>
+      <c r="L59" s="67"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="12"/>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12"/>
-      <c r="L60" s="13"/>
+      <c r="A60" s="65"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="66"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="66"/>
+      <c r="K60" s="66"/>
+      <c r="L60" s="67"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="14"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="16"/>
+      <c r="A61" s="68"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="69"/>
+      <c r="F61" s="69"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="69"/>
+      <c r="I61" s="69"/>
+      <c r="J61" s="69"/>
+      <c r="K61" s="69"/>
+      <c r="L61" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="L41:L42"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="K27:K28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
+  <mergeCells count="134">
+    <mergeCell ref="K27:K42"/>
+    <mergeCell ref="L27:L42"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A55:L61"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:B53"/>
+    <mergeCell ref="C52:D53"/>
+    <mergeCell ref="E52:F53"/>
+    <mergeCell ref="G52:H53"/>
+    <mergeCell ref="I52:J53"/>
+    <mergeCell ref="K52:L53"/>
+    <mergeCell ref="A49:B50"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:F50"/>
+    <mergeCell ref="G49:H50"/>
+    <mergeCell ref="I49:J50"/>
+    <mergeCell ref="K49:L50"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="I46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="L46:L47"/>
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A44:B45"/>
     <mergeCell ref="C44:D45"/>
@@ -2433,37 +2393,91 @@
     <mergeCell ref="I37:J38"/>
     <mergeCell ref="A39:B40"/>
     <mergeCell ref="C39:D40"/>
-    <mergeCell ref="A49:B50"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:F50"/>
-    <mergeCell ref="G49:H50"/>
-    <mergeCell ref="I49:J50"/>
-    <mergeCell ref="K49:L50"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D47"/>
-    <mergeCell ref="E46:F47"/>
-    <mergeCell ref="G46:H47"/>
-    <mergeCell ref="I46:L47"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A54:L54"/>
-    <mergeCell ref="A55:L61"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:B53"/>
-    <mergeCell ref="C52:D53"/>
-    <mergeCell ref="E52:F53"/>
-    <mergeCell ref="G52:H53"/>
-    <mergeCell ref="I52:J53"/>
-    <mergeCell ref="K52:L53"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="K33:K34"/>
-    <mergeCell ref="L33:L34"/>
-    <mergeCell ref="K35:K36"/>
-    <mergeCell ref="L35:L36"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J42"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/09.Stacking.xlsx
+++ b/src/assets/worklog/09.Stacking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD805008-2FA6-455E-B93E-8D6F600E5E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6E5BD6-2695-45B3-B2F6-FC139168C831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="195" windowWidth="25260" windowHeight="15045" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
+    <workbookView xWindow="1500" yWindow="150" windowWidth="25260" windowHeight="15135" xr2:uid="{F083099F-8B17-4B0D-8564-B6DB029B0CC9}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -502,7 +502,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -746,27 +745,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -776,6 +754,189 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,173 +961,11 @@
     <xf numFmtId="41" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1345,17 +1344,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1367,983 +1366,1093 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="12"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9" t="s">
+      <c r="F7" s="55"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9" t="s">
+      <c r="B9" s="55"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9" t="s">
+      <c r="F9" s="55"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="55"/>
+      <c r="K9" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="8"/>
+      <c r="L9" s="75"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="12"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="55"/>
+      <c r="C12" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="67"/>
+      <c r="E12" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="67"/>
+      <c r="G12" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="13" t="s">
+      <c r="H12" s="55"/>
+      <c r="I12" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="9" t="s">
+      <c r="J12" s="67"/>
+      <c r="K12" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="9"/>
+      <c r="L12" s="55"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="A15" s="71"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="14" t="s">
+      <c r="B16" s="68"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="14" t="s">
+      <c r="F16" s="68"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="3" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="3" t="s">
+      <c r="F18" s="15"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="12"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="21" t="s">
+      <c r="B21" s="55"/>
+      <c r="C21" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="25" t="s">
+      <c r="D21" s="60"/>
+      <c r="E21" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="26"/>
-      <c r="G21" s="21" t="s">
+      <c r="F21" s="64"/>
+      <c r="G21" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="22"/>
-      <c r="I21" s="25" t="s">
+      <c r="H21" s="60"/>
+      <c r="I21" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="13" t="s">
+      <c r="J21" s="64"/>
+      <c r="K21" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="13"/>
+      <c r="L21" s="67"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="32" t="s">
+      <c r="B25" s="55"/>
+      <c r="C25" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32" t="s">
+      <c r="D25" s="56"/>
+      <c r="E25" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="33" t="s">
+      <c r="F25" s="56"/>
+      <c r="G25" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="33"/>
-      <c r="I25" s="34" t="s">
+      <c r="H25" s="57"/>
+      <c r="I25" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="34"/>
-      <c r="K25" s="29" t="s">
+      <c r="J25" s="58"/>
+      <c r="K25" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="L25" s="30" t="s">
+      <c r="L25" s="53" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="73"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="71"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="48"/>
       <c r="K27" s="77"/>
       <c r="L27" s="77"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="71"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="48"/>
       <c r="K28" s="78"/>
       <c r="L28" s="78"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="74"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="50"/>
       <c r="K29" s="78"/>
       <c r="L29" s="78"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="74"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="50"/>
       <c r="K30" s="78"/>
       <c r="L30" s="78"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="71"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="48"/>
       <c r="K31" s="78"/>
       <c r="L31" s="78"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="71"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="48"/>
       <c r="K32" s="78"/>
       <c r="L32" s="78"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="71"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="48"/>
       <c r="K33" s="78"/>
       <c r="L33" s="78"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="71"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="48"/>
       <c r="K34" s="78"/>
       <c r="L34" s="78"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="71"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="48"/>
       <c r="K35" s="78"/>
       <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="71"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="48"/>
       <c r="K36" s="78"/>
       <c r="L36" s="78"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="74"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="50"/>
       <c r="K37" s="78"/>
       <c r="L37" s="78"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="74"/>
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="50"/>
       <c r="K38" s="78"/>
       <c r="L38" s="78"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="71"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="48"/>
       <c r="K39" s="78"/>
       <c r="L39" s="78"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="71"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="48"/>
       <c r="K40" s="78"/>
       <c r="L40" s="78"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="71"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="48"/>
       <c r="K41" s="78"/>
       <c r="L41" s="78"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="71"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="48"/>
       <c r="K42" s="79"/>
       <c r="L42" s="79"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="76"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="40"/>
     </row>
     <row r="44" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="44" t="s">
+      <c r="B44" s="30"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="44" t="s">
+      <c r="F44" s="42"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="J44" s="48"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="41"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="26"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="38"/>
-      <c r="B45" s="39"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="43"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="27"/>
+      <c r="L45" s="28"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="36" t="s">
+      <c r="B46" s="30"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F46" s="37"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="59" t="s">
+      <c r="F46" s="30"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="J46" s="48"/>
-      <c r="K46" s="60"/>
-      <c r="L46" s="60"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="38"/>
-      <c r="B47" s="39"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="61"/>
-      <c r="L47" s="61"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="38"/>
+      <c r="L47" s="38"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="12"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="5"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="51" t="s">
+      <c r="A49" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="52"/>
-      <c r="C49" s="55" t="s">
+      <c r="B49" s="18"/>
+      <c r="C49" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="56"/>
-      <c r="E49" s="51" t="s">
+      <c r="D49" s="22"/>
+      <c r="E49" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F49" s="52"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="51" t="s">
+      <c r="F49" s="18"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="J49" s="52"/>
-      <c r="K49" s="55" t="s">
+      <c r="J49" s="18"/>
+      <c r="K49" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="L49" s="56"/>
+      <c r="L49" s="22"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="53"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="54"/>
-      <c r="K50" s="57"/>
-      <c r="L50" s="58"/>
+      <c r="A50" s="19"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="23"/>
+      <c r="L50" s="24"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="12"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="5"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="31" t="s">
+      <c r="B52" s="15"/>
+      <c r="C52" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D52" s="31"/>
-      <c r="E52" s="3" t="s">
+      <c r="D52" s="16"/>
+      <c r="E52" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="31" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="H52" s="31"/>
-      <c r="I52" s="3" t="s">
+      <c r="H52" s="16"/>
+      <c r="I52" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="31" t="s">
+      <c r="J52" s="15"/>
+      <c r="K52" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L52" s="31"/>
+      <c r="L52" s="16"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="12"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="5"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="62" t="s">
+      <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
-      <c r="I55" s="63"/>
-      <c r="J55" s="63"/>
-      <c r="K55" s="63"/>
-      <c r="L55" s="64"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="8"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="65"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="66"/>
-      <c r="D56" s="66"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
-      <c r="J56" s="66"/>
-      <c r="K56" s="66"/>
-      <c r="L56" s="67"/>
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="11"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="65"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66"/>
-      <c r="J57" s="66"/>
-      <c r="K57" s="66"/>
-      <c r="L57" s="67"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="11"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="65"/>
-      <c r="B58" s="66"/>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="66"/>
-      <c r="G58" s="66"/>
-      <c r="H58" s="66"/>
-      <c r="I58" s="66"/>
-      <c r="J58" s="66"/>
-      <c r="K58" s="66"/>
-      <c r="L58" s="67"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="11"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="65"/>
-      <c r="B59" s="66"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="66"/>
-      <c r="K59" s="66"/>
-      <c r="L59" s="67"/>
+      <c r="A59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="11"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="65"/>
-      <c r="B60" s="66"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="66"/>
-      <c r="L60" s="67"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="11"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="68"/>
-      <c r="B61" s="69"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="69"/>
-      <c r="G61" s="69"/>
-      <c r="H61" s="69"/>
-      <c r="I61" s="69"/>
-      <c r="J61" s="69"/>
-      <c r="K61" s="69"/>
-      <c r="L61" s="70"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="134">
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="G18:H19"/>
+    <mergeCell ref="I18:J19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A44:B45"/>
+    <mergeCell ref="C44:D45"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="G44:H45"/>
+    <mergeCell ref="I44:J45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="G37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="A39:B40"/>
     <mergeCell ref="K27:K42"/>
     <mergeCell ref="L27:L42"/>
     <mergeCell ref="A54:L54"/>
@@ -2368,116 +2477,6 @@
     <mergeCell ref="A48:L48"/>
     <mergeCell ref="I46:J47"/>
     <mergeCell ref="K46:K47"/>
-    <mergeCell ref="L46:L47"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A44:B45"/>
-    <mergeCell ref="C44:D45"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="G44:H45"/>
-    <mergeCell ref="I44:J45"/>
-    <mergeCell ref="K44:L45"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
-    <mergeCell ref="A37:B38"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:F38"/>
-    <mergeCell ref="G37:H38"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="A39:B40"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="G18:H19"/>
-    <mergeCell ref="I18:J19"/>
-    <mergeCell ref="K18:L19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:F42"/>
-    <mergeCell ref="G41:H42"/>
-    <mergeCell ref="I41:J42"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
